--- a/AC_2023/AC_032_32-Husnabad.xlsx
+++ b/AC_2023/AC_032_32-Husnabad.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,14 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,8 +60,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -77,11 +101,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +168,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA308"/>
+  <dimension ref="A1:AA310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3421,7 +3504,11 @@
       <c r="A38" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="4" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>GOVARDHANAGIRI</t>
+        </is>
+      </c>
       <c r="C38" s="5" t="n">
         <v>4</v>
       </c>
@@ -4449,7 +4536,11 @@
       <c r="A50" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>IGANDIPALLI</t>
+        </is>
+      </c>
       <c r="C50" s="5" t="n">
         <v>8</v>
       </c>
@@ -6423,7 +6514,11 @@
       <c r="A73" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>MIRZAPLIR</t>
+        </is>
+      </c>
       <c r="C73" s="5" t="n">
         <v>0</v>
       </c>
@@ -15621,7 +15716,11 @@
       <c r="A180" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="B180" s="4" t="inlineStr"/>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>VENNAMPALLI</t>
+        </is>
+      </c>
       <c r="C180" s="5" t="n">
         <v>6</v>
       </c>
@@ -17079,7 +17178,11 @@
       <c r="A197" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="B197" s="4" t="inlineStr"/>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>PERKAPALLI HIO</t>
+        </is>
+      </c>
       <c r="C197" s="5" t="n">
         <v>4</v>
       </c>
@@ -18881,7 +18984,11 @@
       <c r="A218" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="B218" s="4" t="inlineStr"/>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>MANGALAPALL HIO</t>
+        </is>
+      </c>
       <c r="C218" s="5" t="n">
         <v>7</v>
       </c>
@@ -26614,110 +26721,301 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B308" s="7" t="inlineStr"/>
-      <c r="C308" s="8">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B308" s="10" t="inlineStr"/>
+      <c r="C308" s="11">
         <f>SUM(C6:C307)</f>
         <v/>
       </c>
-      <c r="D308" s="8">
+      <c r="D308" s="11">
         <f>SUM(D6:D307)</f>
         <v/>
       </c>
-      <c r="E308" s="8">
+      <c r="E308" s="11">
         <f>SUM(E6:E307)</f>
         <v/>
       </c>
-      <c r="F308" s="8">
+      <c r="F308" s="11">
         <f>SUM(F6:F307)</f>
         <v/>
       </c>
-      <c r="G308" s="8">
+      <c r="G308" s="11">
         <f>SUM(G6:G307)</f>
         <v/>
       </c>
-      <c r="H308" s="8">
+      <c r="H308" s="11">
         <f>SUM(H6:H307)</f>
         <v/>
       </c>
-      <c r="I308" s="8">
+      <c r="I308" s="11">
         <f>SUM(I6:I307)</f>
         <v/>
       </c>
-      <c r="J308" s="8">
+      <c r="J308" s="11">
         <f>SUM(J6:J307)</f>
         <v/>
       </c>
-      <c r="K308" s="8">
+      <c r="K308" s="11">
         <f>SUM(K6:K307)</f>
         <v/>
       </c>
-      <c r="L308" s="8">
+      <c r="L308" s="11">
         <f>SUM(L6:L307)</f>
         <v/>
       </c>
-      <c r="M308" s="8">
+      <c r="M308" s="11">
         <f>SUM(M6:M307)</f>
         <v/>
       </c>
-      <c r="N308" s="8">
+      <c r="N308" s="11">
         <f>SUM(N6:N307)</f>
         <v/>
       </c>
-      <c r="O308" s="8">
+      <c r="O308" s="11">
         <f>SUM(O6:O307)</f>
         <v/>
       </c>
-      <c r="P308" s="8">
+      <c r="P308" s="11">
         <f>SUM(P6:P307)</f>
         <v/>
       </c>
-      <c r="Q308" s="8">
+      <c r="Q308" s="11">
         <f>SUM(Q6:Q307)</f>
         <v/>
       </c>
-      <c r="R308" s="8">
+      <c r="R308" s="11">
         <f>SUM(R6:R307)</f>
         <v/>
       </c>
-      <c r="S308" s="8">
+      <c r="S308" s="11">
         <f>SUM(S6:S307)</f>
         <v/>
       </c>
-      <c r="T308" s="8">
+      <c r="T308" s="11">
         <f>SUM(T6:T307)</f>
         <v/>
       </c>
-      <c r="U308" s="8">
+      <c r="U308" s="11">
         <f>SUM(U6:U307)</f>
         <v/>
       </c>
-      <c r="V308" s="8">
+      <c r="V308" s="11">
         <f>SUM(V6:V307)</f>
         <v/>
       </c>
-      <c r="W308" s="8">
+      <c r="W308" s="11">
         <f>SUM(W6:W307)</f>
         <v/>
       </c>
-      <c r="X308" s="8">
+      <c r="X308" s="11">
         <f>SUM(X6:X307)</f>
         <v/>
       </c>
-      <c r="Y308" s="8">
+      <c r="Y308" s="11">
         <f>SUM(Y6:Y307)</f>
         <v/>
       </c>
-      <c r="Z308" s="8">
+      <c r="Z308" s="11">
         <f>SUM(Z6:Z307)</f>
         <v/>
       </c>
-      <c r="AA308" s="8">
-        <f>SUM(C308:U308)-V308</f>
+      <c r="AA308" s="11">
+        <f>SUM(AA6:AA307)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="12" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B309" s="13" t="inlineStr"/>
+      <c r="C309" s="14" t="n">
+        <v>330</v>
+      </c>
+      <c r="D309" s="14" t="n">
+        <v>8459</v>
+      </c>
+      <c r="E309" s="14" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F309" s="14" t="n">
+        <v>4295</v>
+      </c>
+      <c r="G309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V309" s="14" t="n">
+        <v>15100</v>
+      </c>
+      <c r="W309" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="X309" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="Y309" s="14" t="n">
+        <v>15246</v>
+      </c>
+      <c r="Z309" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B310" s="16" t="inlineStr"/>
+      <c r="C310" s="17">
+        <f>C308+C309</f>
+        <v/>
+      </c>
+      <c r="D310" s="17">
+        <f>D308+D309</f>
+        <v/>
+      </c>
+      <c r="E310" s="17">
+        <f>E308+E309</f>
+        <v/>
+      </c>
+      <c r="F310" s="17">
+        <f>F308+F309</f>
+        <v/>
+      </c>
+      <c r="G310" s="17">
+        <f>G308+G309</f>
+        <v/>
+      </c>
+      <c r="H310" s="17">
+        <f>H308+H309</f>
+        <v/>
+      </c>
+      <c r="I310" s="17">
+        <f>I308+I309</f>
+        <v/>
+      </c>
+      <c r="J310" s="17">
+        <f>J308+J309</f>
+        <v/>
+      </c>
+      <c r="K310" s="17">
+        <f>K308+K309</f>
+        <v/>
+      </c>
+      <c r="L310" s="17">
+        <f>L308+L309</f>
+        <v/>
+      </c>
+      <c r="M310" s="17">
+        <f>M308+M309</f>
+        <v/>
+      </c>
+      <c r="N310" s="17">
+        <f>N308+N309</f>
+        <v/>
+      </c>
+      <c r="O310" s="17">
+        <f>O308+O309</f>
+        <v/>
+      </c>
+      <c r="P310" s="17">
+        <f>P308+P309</f>
+        <v/>
+      </c>
+      <c r="Q310" s="17">
+        <f>Q308+Q309</f>
+        <v/>
+      </c>
+      <c r="R310" s="17">
+        <f>R308+R309</f>
+        <v/>
+      </c>
+      <c r="S310" s="17">
+        <f>S308+S309</f>
+        <v/>
+      </c>
+      <c r="T310" s="17">
+        <f>T308+T309</f>
+        <v/>
+      </c>
+      <c r="U310" s="17">
+        <f>U308+U309</f>
+        <v/>
+      </c>
+      <c r="V310" s="17">
+        <f>V308+V309</f>
+        <v/>
+      </c>
+      <c r="W310" s="17">
+        <f>W308+W309</f>
+        <v/>
+      </c>
+      <c r="X310" s="17">
+        <f>X308+X309</f>
+        <v/>
+      </c>
+      <c r="Y310" s="17">
+        <f>Y308+Y309</f>
+        <v/>
+      </c>
+      <c r="Z310" s="17">
+        <f>Z308+Z309</f>
+        <v/>
+      </c>
+      <c r="AA310" s="17">
+        <f>AA308+AA309</f>
         <v/>
       </c>
     </row>
